--- a/Assets/Data/Excel/tower.xlsx
+++ b/Assets/Data/Excel/tower.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Cube\Assets\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE47626B-C84D-4EB0-9EDC-1BA026974498}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D5DBBC1-6FA5-4A1C-84CB-205A1CF1AED2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="42">
   <si>
     <t>##var</t>
   </si>
@@ -133,6 +133,26 @@
   </si>
   <si>
     <t>Assets/Arts/Tower/IceTower.prefab</t>
+  </si>
+  <si>
+    <t>Assets/Arts/Effects/BowAttackEffect.prefab</t>
+  </si>
+  <si>
+    <t>Assets/Arts/Effects/BowHitEffect.prefab</t>
+  </si>
+  <si>
+    <t>Assets/Arts/Effects/IceAttackEffect.prefab</t>
+  </si>
+  <si>
+    <t>Assets/Arts/Effects/IceHitEffect.prefab</t>
+  </si>
+  <si>
+    <t>attackEffect</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>hitEffect</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -362,7 +382,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="2" width="10" customWidth="1"/>
@@ -373,9 +393,11 @@
     <col min="7" max="8" width="14" customWidth="1"/>
     <col min="9" max="10" width="12" customWidth="1"/>
     <col min="11" max="11" width="16" customWidth="1"/>
+    <col min="12" max="12" width="45.125" customWidth="1"/>
+    <col min="13" max="13" width="35.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="21.95" customHeight="1">
+    <row r="1" spans="1:13" ht="21.95" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -409,8 +431,14 @@
       <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
+      <c r="L1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>41</v>
+      </c>
     </row>
-    <row r="2" spans="1:11" ht="21.95" customHeight="1">
+    <row r="2" spans="1:13" ht="21.95" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
@@ -444,8 +472,14 @@
       <c r="K2" s="1" t="s">
         <v>14</v>
       </c>
+      <c r="L2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="3" spans="1:11" ht="21.95" customHeight="1">
+    <row r="3" spans="1:13" ht="21.95" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>15</v>
       </c>
@@ -479,8 +513,14 @@
       <c r="K3" s="1" t="s">
         <v>16</v>
       </c>
+      <c r="L3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="4" spans="1:11" ht="21.95" customHeight="1">
+    <row r="4" spans="1:13" ht="21.95" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>17</v>
       </c>
@@ -514,8 +554,14 @@
       <c r="K4" s="1" t="s">
         <v>27</v>
       </c>
+      <c r="L4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>22</v>
+      </c>
     </row>
-    <row r="5" spans="1:11" ht="27.95" customHeight="1">
+    <row r="5" spans="1:13" ht="27.95" customHeight="1">
       <c r="A5" s="2"/>
       <c r="B5" s="2">
         <v>1001</v>
@@ -542,13 +588,19 @@
         <v>3.5</v>
       </c>
       <c r="J5" s="2">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="K5" s="2">
         <v>1</v>
       </c>
+      <c r="L5" t="s">
+        <v>36</v>
+      </c>
+      <c r="M5" t="s">
+        <v>37</v>
+      </c>
     </row>
-    <row r="6" spans="1:11" ht="27.95" customHeight="1">
+    <row r="6" spans="1:13" ht="27.95" customHeight="1">
       <c r="A6" s="2"/>
       <c r="B6" s="2">
         <v>1002</v>
@@ -580,8 +632,14 @@
       <c r="K6" s="2">
         <v>1.8</v>
       </c>
+      <c r="L6" t="s">
+        <v>38</v>
+      </c>
+      <c r="M6" t="s">
+        <v>39</v>
+      </c>
     </row>
-    <row r="7" spans="1:11" ht="27.95" customHeight="1">
+    <row r="7" spans="1:13" ht="27.95" customHeight="1">
       <c r="A7" s="2"/>
       <c r="B7" s="2">
         <v>1003</v>
@@ -612,6 +670,12 @@
       </c>
       <c r="K7" s="2">
         <v>1.2</v>
+      </c>
+      <c r="L7" t="s">
+        <v>38</v>
+      </c>
+      <c r="M7" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Excel/tower.xlsx
+++ b/Assets/Data/Excel/tower.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Cube\Assets\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D5DBBC1-6FA5-4A1C-84CB-205A1CF1AED2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{885917F7-D34F-4B42-B7EE-C160CB61B211}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="43">
   <si>
     <t>##var</t>
   </si>
@@ -127,9 +127,6 @@
   </si>
   <si>
     <t>控制型塔，当前阶段可先做低伤害，减速后续再接</t>
-  </si>
-  <si>
-    <t>Assets/Arts/Tower/NormalTower.prefab</t>
   </si>
   <si>
     <t>Assets/Arts/Tower/IceTower.prefab</t>
@@ -152,6 +149,14 @@
   </si>
   <si>
     <t>hitEffect</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Arts/Tower/NormalTower.prefab</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>upgrade</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -382,7 +387,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:O7"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="2" width="10" customWidth="1"/>
@@ -392,12 +397,12 @@
     <col min="6" max="6" width="42" customWidth="1"/>
     <col min="7" max="8" width="14" customWidth="1"/>
     <col min="9" max="10" width="12" customWidth="1"/>
-    <col min="11" max="11" width="16" customWidth="1"/>
-    <col min="12" max="12" width="45.125" customWidth="1"/>
-    <col min="13" max="13" width="35.625" customWidth="1"/>
+    <col min="11" max="12" width="16" customWidth="1"/>
+    <col min="13" max="13" width="45.125" customWidth="1"/>
+    <col min="14" max="14" width="35.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="21.95" customHeight="1">
+    <row r="1" spans="1:15" ht="21.95" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -431,14 +436,18 @@
       <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="1"/>
+      <c r="M1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="M1" s="1" t="s">
-        <v>41</v>
+      <c r="O1" s="1" t="s">
+        <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="21.95" customHeight="1">
+    <row r="2" spans="1:15" ht="21.95" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
@@ -472,14 +481,15 @@
       <c r="K2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="L2" s="1" t="s">
-        <v>13</v>
-      </c>
+      <c r="L2" s="1"/>
       <c r="M2" s="1" t="s">
         <v>13</v>
       </c>
+      <c r="N2" s="1" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="3" spans="1:13" ht="21.95" customHeight="1">
+    <row r="3" spans="1:15" ht="21.95" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>15</v>
       </c>
@@ -513,14 +523,15 @@
       <c r="K3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="L3" s="1" t="s">
-        <v>16</v>
-      </c>
+      <c r="L3" s="1"/>
       <c r="M3" s="1" t="s">
         <v>16</v>
       </c>
+      <c r="N3" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="4" spans="1:13" ht="21.95" customHeight="1">
+    <row r="4" spans="1:15" ht="21.95" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>17</v>
       </c>
@@ -554,14 +565,15 @@
       <c r="K4" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="L4" s="1" t="s">
-        <v>22</v>
-      </c>
+      <c r="L4" s="1"/>
       <c r="M4" s="1" t="s">
         <v>22</v>
       </c>
+      <c r="N4" s="1" t="s">
+        <v>22</v>
+      </c>
     </row>
-    <row r="5" spans="1:13" ht="27.95" customHeight="1">
+    <row r="5" spans="1:15" ht="27.95" customHeight="1">
       <c r="A5" s="2"/>
       <c r="B5" s="2">
         <v>1001</v>
@@ -576,7 +588,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="G5" s="2">
         <v>1</v>
@@ -593,14 +605,15 @@
       <c r="K5" s="2">
         <v>1</v>
       </c>
-      <c r="L5" t="s">
+      <c r="L5" s="2"/>
+      <c r="M5" t="s">
+        <v>35</v>
+      </c>
+      <c r="N5" t="s">
         <v>36</v>
       </c>
-      <c r="M5" t="s">
-        <v>37</v>
-      </c>
     </row>
-    <row r="6" spans="1:13" ht="27.95" customHeight="1">
+    <row r="6" spans="1:15" ht="27.95" customHeight="1">
       <c r="A6" s="2"/>
       <c r="B6" s="2">
         <v>1002</v>
@@ -615,7 +628,7 @@
         <v>2</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G6" s="2">
         <v>1</v>
@@ -632,14 +645,15 @@
       <c r="K6" s="2">
         <v>1.8</v>
       </c>
-      <c r="L6" t="s">
+      <c r="L6" s="2"/>
+      <c r="M6" t="s">
+        <v>37</v>
+      </c>
+      <c r="N6" t="s">
         <v>38</v>
       </c>
-      <c r="M6" t="s">
-        <v>39</v>
-      </c>
     </row>
-    <row r="7" spans="1:13" ht="27.95" customHeight="1">
+    <row r="7" spans="1:15" ht="27.95" customHeight="1">
       <c r="A7" s="2"/>
       <c r="B7" s="2">
         <v>1003</v>
@@ -654,7 +668,7 @@
         <v>3</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G7" s="2">
         <v>1</v>
@@ -671,11 +685,12 @@
       <c r="K7" s="2">
         <v>1.2</v>
       </c>
-      <c r="L7" t="s">
+      <c r="L7" s="2"/>
+      <c r="M7" t="s">
+        <v>37</v>
+      </c>
+      <c r="N7" t="s">
         <v>38</v>
-      </c>
-      <c r="M7" t="s">
-        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Excel/tower.xlsx
+++ b/Assets/Data/Excel/tower.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Cube\Assets\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{885917F7-D34F-4B42-B7EE-C160CB61B211}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AB1F734-4C44-4D17-919D-D32FE8ABC8F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9600" yWindow="0" windowWidth="28800" windowHeight="15435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="tower" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="60">
   <si>
     <t>##var</t>
   </si>
@@ -117,15 +117,9 @@
     <t>基础单体塔，造价低，攻速较快</t>
   </si>
   <si>
-    <t>炮塔</t>
-  </si>
-  <si>
     <t>高伤害塔，适合以后扩展AOE，现在可先按单体瞬间伤害处理</t>
   </si>
   <si>
-    <t>冰塔</t>
-  </si>
-  <si>
     <t>控制型塔，当前阶段可先做低伤害，减速后续再接</t>
   </si>
   <si>
@@ -156,7 +150,82 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>upgrade</t>
+    <t>冰霜塔</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>火焰塔</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>雷电塔</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>毒液塔</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>unlockLevel</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>解锁等级</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>是否激活</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>bool</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>enable</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>upgradeCost</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SellGoldRate</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>canUpgrade</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>升级所需金币</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>出售返还金币的比例</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>升级</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>iconLocation</t>
+  </si>
+  <si>
+    <t>ui_td_tower_arrow_icon</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ui_td_tower_fire_icon</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ui_td_tower_ice_icon</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ui_td_tower_cannon_icon</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -164,7 +233,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -183,6 +252,14 @@
       <sz val="9"/>
       <name val="宋体"/>
       <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -212,12 +289,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -387,22 +467,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O7"/>
+  <dimension ref="A1:S29"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="2" width="10" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="44" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="42" customWidth="1"/>
+    <col min="6" max="6" width="30" customWidth="1"/>
     <col min="7" max="8" width="14" customWidth="1"/>
     <col min="9" max="10" width="12" customWidth="1"/>
-    <col min="11" max="12" width="16" customWidth="1"/>
-    <col min="13" max="13" width="45.125" customWidth="1"/>
-    <col min="14" max="14" width="35.625" customWidth="1"/>
+    <col min="11" max="13" width="16" customWidth="1"/>
+    <col min="14" max="14" width="45.125" customWidth="1"/>
+    <col min="15" max="15" width="35.625" customWidth="1"/>
+    <col min="16" max="16" width="16" customWidth="1"/>
+    <col min="17" max="17" width="18.625" customWidth="1"/>
+    <col min="18" max="18" width="16" customWidth="1"/>
+    <col min="19" max="19" width="68" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="21.95" customHeight="1">
+    <row r="1" spans="1:19" ht="21.95" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -436,18 +520,32 @@
       <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1"/>
+      <c r="L1" s="1" t="s">
+        <v>44</v>
+      </c>
       <c r="M1" s="1" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>42</v>
+        <v>38</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>55</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="21.95" customHeight="1">
+    <row r="2" spans="1:19" ht="21.95" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
@@ -481,15 +579,32 @@
       <c r="K2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="L2" s="1"/>
+      <c r="L2" s="1" t="s">
+        <v>12</v>
+      </c>
       <c r="M2" s="1" t="s">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="N2" s="1" t="s">
         <v>13</v>
       </c>
+      <c r="O2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="3" spans="1:15" ht="21.95" customHeight="1">
+    <row r="3" spans="1:19" ht="21.95" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>15</v>
       </c>
@@ -523,15 +638,32 @@
       <c r="K3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="L3" s="1"/>
+      <c r="L3" s="1" t="s">
+        <v>16</v>
+      </c>
       <c r="M3" s="1" t="s">
         <v>16</v>
       </c>
       <c r="N3" s="1" t="s">
         <v>16</v>
       </c>
+      <c r="O3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="S3" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="4" spans="1:15" ht="21.95" customHeight="1">
+    <row r="4" spans="1:19" ht="21.95" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>17</v>
       </c>
@@ -565,15 +697,32 @@
       <c r="K4" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="L4" s="1"/>
+      <c r="L4" s="3" t="s">
+        <v>45</v>
+      </c>
       <c r="M4" s="1" t="s">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="N4" s="1" t="s">
         <v>22</v>
       </c>
+      <c r="O4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P4" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q4" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="R4" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="S4" s="1" t="s">
+        <v>22</v>
+      </c>
     </row>
-    <row r="5" spans="1:15" ht="27.95" customHeight="1">
+    <row r="5" spans="1:19" ht="27.95" customHeight="1">
       <c r="A5" s="2"/>
       <c r="B5" s="2">
         <v>1001</v>
@@ -588,7 +737,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G5" s="2">
         <v>1</v>
@@ -605,30 +754,47 @@
       <c r="K5" s="2">
         <v>1</v>
       </c>
-      <c r="L5" s="2"/>
-      <c r="M5" t="s">
-        <v>35</v>
-      </c>
-      <c r="N5" t="s">
-        <v>36</v>
+      <c r="L5" s="2">
+        <v>1</v>
+      </c>
+      <c r="M5" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="P5">
+        <v>100</v>
+      </c>
+      <c r="Q5">
+        <v>9</v>
+      </c>
+      <c r="R5" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="S5" s="2" t="s">
+        <v>56</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="27.95" customHeight="1">
+    <row r="6" spans="1:19" ht="27.95" customHeight="1">
       <c r="A6" s="2"/>
       <c r="B6" s="2">
         <v>1002</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>30</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>31</v>
       </c>
       <c r="E6" s="2">
         <v>2</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G6" s="2">
         <v>1</v>
@@ -645,30 +811,47 @@
       <c r="K6" s="2">
         <v>1.8</v>
       </c>
-      <c r="L6" s="2"/>
-      <c r="M6" t="s">
-        <v>37</v>
-      </c>
-      <c r="N6" t="s">
-        <v>38</v>
+      <c r="L6" s="2">
+        <v>1</v>
+      </c>
+      <c r="M6" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="N6" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="O6" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="P6">
+        <v>100</v>
+      </c>
+      <c r="Q6">
+        <v>9</v>
+      </c>
+      <c r="R6" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="S6" s="2" t="s">
+        <v>57</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="27.95" customHeight="1">
+    <row r="7" spans="1:19" ht="24" customHeight="1">
       <c r="A7" s="2"/>
       <c r="B7" s="2">
         <v>1003</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E7" s="2">
         <v>3</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G7" s="2">
         <v>1</v>
@@ -685,13 +868,145 @@
       <c r="K7" s="2">
         <v>1.2</v>
       </c>
-      <c r="L7" s="2"/>
-      <c r="M7" t="s">
-        <v>37</v>
-      </c>
-      <c r="N7" t="s">
-        <v>38</v>
-      </c>
+      <c r="L7" s="2">
+        <v>1</v>
+      </c>
+      <c r="M7" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="N7" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="P7">
+        <v>100</v>
+      </c>
+      <c r="Q7">
+        <v>9</v>
+      </c>
+      <c r="R7" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="S7" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19">
+      <c r="B8" s="2">
+        <v>1004</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E8" s="2">
+        <v>4</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G8" s="2">
+        <v>1</v>
+      </c>
+      <c r="H8" s="2">
+        <v>150</v>
+      </c>
+      <c r="I8" s="2">
+        <v>3.2</v>
+      </c>
+      <c r="J8" s="2">
+        <v>5</v>
+      </c>
+      <c r="K8" s="2">
+        <v>1.2</v>
+      </c>
+      <c r="L8" s="2">
+        <v>1</v>
+      </c>
+      <c r="M8" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="N8" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="O8" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="P8">
+        <v>100</v>
+      </c>
+      <c r="Q8">
+        <v>9</v>
+      </c>
+      <c r="R8" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="S8" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19">
+      <c r="B9" s="2">
+        <v>1005</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E9" s="2">
+        <v>5</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G9" s="2">
+        <v>1</v>
+      </c>
+      <c r="H9" s="2">
+        <v>150</v>
+      </c>
+      <c r="I9" s="2">
+        <v>3.2</v>
+      </c>
+      <c r="J9" s="2">
+        <v>5</v>
+      </c>
+      <c r="K9" s="2">
+        <v>1.2</v>
+      </c>
+      <c r="L9" s="2">
+        <v>1</v>
+      </c>
+      <c r="M9" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="N9" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="O9" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="P9">
+        <v>100</v>
+      </c>
+      <c r="Q9">
+        <v>9</v>
+      </c>
+      <c r="R9" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="S9" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="29" spans="14:14" ht="15">
+      <c r="N29" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
